--- a/code/Created Files for Analysis/missingness_uebersicht.xlsx
+++ b/code/Created Files for Analysis/missingness_uebersicht.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -380,61 +380,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FM.LBL.BMNY.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AUT, BEL, CYP, DEU, ESP, EST, FIN, FRA, GRC, HRV, IRL, ITA, LTU, LUX, LVA, MLT, NLD, PRT, SVK, SVN</t>
+          <t>BEN, CHN, GIN, HKG, MNE, MRT, NER, NGA, PAK, SLE, TCD, VEN, VNM, YEM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>IMF-GDD-CG</t>
         </is>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>11.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BEN, CHN, GIN, HKG, MNE, MRT, NER, NGA, PAK, SLE, TCD, VEN, VNM, YEM</t>
+          <t>ARE, CHN, EGY, GEO, KHM, NLD, PAN, PHL, TJK, TZA, UZB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMF-GDD-CG</t>
+          <t>WB-CWON-NFA-PC</t>
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARE, CHN, EGY, GEO, KHM, NLD, PAN, PHL, TJK, TZA, UZB</t>
+          <t>AFG, CYP, HKG, ISR, MNE, NZL, SRB, UZB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WB-CWON-NFA-PC</t>
+          <t>WB-CWON-PCA-PC</t>
         </is>
       </c>
       <c r="B5">
@@ -452,25 +452,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WB-CWON-PCA-PC</t>
+          <t>WB-WDI-NE-GDI-TOTL-KD</t>
         </is>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AFG, CYP, HKG, ISR, MNE, NZL, SRB, UZB</t>
+          <t>AFG, MWI, NGA, VEN, YEM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-GDI-TOTL-KD</t>
+          <t>WB-WDI-SE-XPD-TOTL-GD-ZS</t>
         </is>
       </c>
       <c r="B7">
@@ -481,32 +481,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AFG, MWI, NGA, VEN, YEM</t>
+          <t>BIH, IRQ, MKD, MNE, NGA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WB-WDI-SE-XPD-TOTL-GD-ZS</t>
+          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
         </is>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BIH, IRQ, MKD, MNE, NGA</t>
+          <t>ECU, NPL, TCD, TZA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
+          <t>WB-WDI-NE-EXP-GNFS-KD</t>
         </is>
       </c>
       <c r="B9">
@@ -517,32 +517,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ECU, NPL, TCD, TZA</t>
+          <t>AFG, MWI, NGA, VEN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-EXP-GNFS-KD</t>
+          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
         </is>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AFG, MWI, NGA, VEN</t>
+          <t>HKG, MLT, PSE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
+          <t>WB-WDI-TX-VAL-TECH-CD</t>
         </is>
       </c>
       <c r="B11">
@@ -553,14 +553,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HKG, MLT, PSE</t>
+          <t>IRQ, TCD, VEN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB-WDI-TX-VAL-TECH-CD</t>
+          <t>BN.CAB.XOKA.GD.ZS</t>
         </is>
       </c>
       <c r="B12">
@@ -571,32 +571,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IRQ, TCD, VEN</t>
+          <t>ARE, IRN, TCD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BN.CAB.XOKA.GD.ZS</t>
+          <t>WB-WDI-SL-GDP-PCAP-EM-KD</t>
         </is>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARE, IRN, TCD</t>
+          <t>VEN, YEM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-GDP-PCAP-EM-KD</t>
+          <t>WB-WDI-NE-CON-GOVT-CD</t>
         </is>
       </c>
       <c r="B14">
@@ -607,14 +607,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VEN, YEM</t>
+          <t>MWI, NGA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-CON-GOVT-CD</t>
+          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B15">
@@ -625,14 +625,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MWI, NGA</t>
+          <t>CHN, KAZ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
+          <t>SWIID-GINI-DISP</t>
         </is>
       </c>
       <c r="B16">
@@ -643,14 +643,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CHN, KAZ</t>
+          <t>COG, PSE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SWIID-GINI-DISP</t>
+          <t>SWIID-GINI-MKT</t>
         </is>
       </c>
       <c r="B17">
@@ -668,25 +668,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SWIID-GINI-MKT</t>
+          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
         </is>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COG, PSE</t>
+          <t>TCD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-GDP-PCAP-KD</t>
+          <t>WB-WDI-TM-VAL-AGRI-ZS-UN</t>
         </is>
       </c>
       <c r="B19">
@@ -697,14 +697,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>TCD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-GDP-MKTP-KD</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
         </is>
       </c>
       <c r="B20">
@@ -715,14 +715,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>CHN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
+          <t>TT.PRI.MRCH.XD.WD</t>
         </is>
       </c>
       <c r="B21">
@@ -733,86 +733,66 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>MNE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WB-WDI-TM-VAL-AGRI-ZS-UN</t>
+          <t>UNDP-HDI-GNIPC</t>
         </is>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.8</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TCD</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
+          <t>WB-WDI-SL-TLF-TOTL-IN</t>
         </is>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0.8</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TT.PRI.MRCH.XD.WD</t>
+          <t>UNDP-HDI-GDI-GNI-PC-F</t>
         </is>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.8</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MNE</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WB-WDI-GDP-ZG</t>
+          <t>UNDP-HDI-GDI-GNI-PC-M</t>
         </is>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.8</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GNIPC</t>
+          <t>UNDP-HDI-GII-LFPR-F</t>
         </is>
       </c>
       <c r="B26">
@@ -825,7 +805,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-TLF-TOTL-IN</t>
+          <t>UNDP-HDI-GII-LFPR-M</t>
         </is>
       </c>
       <c r="B27">
@@ -838,7 +818,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GDI-GNI-PC-F</t>
+          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
         </is>
       </c>
       <c r="B28">
@@ -851,7 +831,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GDI-GNI-PC-M</t>
+          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
         </is>
       </c>
       <c r="B29">
@@ -864,7 +844,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GII-LFPR-F</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B30">
@@ -877,7 +857,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNDP-HDI-GII-LFPR-M</t>
+          <t>WB-WDI-NY-GDP-PCAP-KD</t>
         </is>
       </c>
       <c r="B31">
@@ -890,7 +870,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WB-WDI-FM-AST-NFRG-CN</t>
+          <t>WB-WDI-NY-GDP-MKTP-KD</t>
         </is>
       </c>
       <c r="B32">
@@ -903,7 +883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
+          <t>FP.CPI.TOTL.ZG</t>
         </is>
       </c>
       <c r="B33">
@@ -916,7 +896,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
+          <t>NY.GDP.DEFL.KD.ZG</t>
         </is>
       </c>
       <c r="B34">
@@ -929,7 +909,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="B35">
@@ -942,39 +922,13 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>WB-WDI-GDP-ZG</t>
         </is>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NY.GDP.DEFL.KD.ZG</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
         <v>0</v>
       </c>
     </row>
@@ -1008,42 +962,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Venezuela, RB</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C4">
@@ -1053,12 +1007,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Venezuela, RB</t>
         </is>
       </c>
       <c r="C5">
@@ -1113,12 +1067,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C9">
@@ -1128,12 +1082,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>West Bank and Gaza</t>
         </is>
       </c>
       <c r="C10">
@@ -1143,12 +1097,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>West Bank and Gaza</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C11">
@@ -1158,12 +1112,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>YEM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Yemen, Rep.</t>
         </is>
       </c>
       <c r="C12">
@@ -1173,27 +1127,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YEM</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yemen, Rep.</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Congo, Rep.</t>
         </is>
       </c>
       <c r="C14">
@@ -1203,12 +1157,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Congo, Rep.</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C15">
@@ -1248,12 +1202,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C18">
@@ -1263,12 +1217,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C19">
@@ -1278,12 +1232,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C20">
@@ -1293,42 +1247,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C23">
@@ -1338,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt, Arab Rep.</t>
         </is>
       </c>
       <c r="C24">
@@ -1353,12 +1307,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C25">
@@ -1368,12 +1322,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C26">
@@ -1383,12 +1337,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Iran, Islamic Rep.</t>
         </is>
       </c>
       <c r="C27">
@@ -1398,12 +1352,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C28">
@@ -1413,12 +1367,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Egypt, Arab Rep.</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C29">
@@ -1428,12 +1382,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C30">
@@ -1443,12 +1397,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C31">
@@ -1458,12 +1412,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C32">
@@ -1473,12 +1427,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C33">
@@ -1488,12 +1442,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C34">
@@ -1503,12 +1457,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C35">
@@ -1518,12 +1472,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C36">
@@ -1533,12 +1487,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C37">
@@ -1548,12 +1502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C38">
@@ -1563,12 +1517,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Iran, Islamic Rep.</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C39">
@@ -1578,12 +1532,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C40">
@@ -1593,12 +1547,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C41">
@@ -1608,267 +1562,267 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Slovak Republic</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C59">
@@ -1878,12 +1832,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C60">
@@ -1893,12 +1847,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C61">
@@ -1908,12 +1862,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C62">
@@ -1923,12 +1877,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C63">
@@ -1938,12 +1892,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C64">
@@ -1953,12 +1907,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C65">
@@ -1968,12 +1922,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C66">
@@ -1983,12 +1937,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C67">
@@ -1998,12 +1952,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C68">
@@ -2013,12 +1967,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C69">
@@ -2028,12 +1982,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C70">
@@ -2043,12 +1997,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C71">
@@ -2058,12 +2012,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C72">
@@ -2073,12 +2027,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C73">
@@ -2088,12 +2042,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C74">
@@ -2103,12 +2057,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C75">
@@ -2118,12 +2072,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C76">
@@ -2133,12 +2087,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C77">
@@ -2148,12 +2102,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C78">
@@ -2163,12 +2117,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C79">
@@ -2178,12 +2132,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C80">
@@ -2193,12 +2147,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C81">
@@ -2208,12 +2162,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C82">
@@ -2223,12 +2177,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C83">
@@ -2238,12 +2192,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Kyrgyz Republic</t>
         </is>
       </c>
       <c r="C84">
@@ -2253,12 +2207,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Korea, Rep.</t>
         </is>
       </c>
       <c r="C85">
@@ -2268,12 +2222,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C86">
@@ -2283,12 +2237,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C87">
@@ -2298,12 +2252,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C88">
@@ -2313,12 +2267,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C89">
@@ -2328,12 +2282,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kyrgyz Republic</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C90">
@@ -2343,12 +2297,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Korea, Rep.</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C91">
@@ -2358,12 +2312,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C92">
@@ -2373,12 +2327,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C93">
@@ -2388,12 +2342,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C94">
@@ -2403,12 +2357,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="C95">
@@ -2418,12 +2372,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C96">
@@ -2433,12 +2387,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C97">
@@ -2448,12 +2402,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C98">
@@ -2463,12 +2417,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C99">
@@ -2478,12 +2432,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C100">
@@ -2493,12 +2447,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C101">
@@ -2508,12 +2462,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C102">
@@ -2523,12 +2477,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Russian Federation</t>
         </is>
       </c>
       <c r="C103">
@@ -2538,12 +2492,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C104">
@@ -2553,12 +2507,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C105">
@@ -2568,12 +2522,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C106">
@@ -2583,12 +2537,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C107">
@@ -2598,12 +2552,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Slovak Republic</t>
         </is>
       </c>
       <c r="C108">
@@ -2613,12 +2567,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C109">
